--- a/data/trans_bre/IP41-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 13,04</t>
+          <t>-8,44; 12,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 10,0</t>
+          <t>-5,75; 10,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 12,78</t>
+          <t>-7,96; 12,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 16,2</t>
+          <t>-9,33; 15,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 11,56</t>
+          <t>-6,07; 12,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 16,69</t>
+          <t>-8,84; 16,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 3,81</t>
+          <t>-7,89; 4,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 10,52</t>
+          <t>-2,41; 11,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 17,39</t>
+          <t>-0,6; 16,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 4,26</t>
+          <t>-8,4; 5,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 12,67</t>
+          <t>-2,61; 13,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 23,9</t>
+          <t>-0,71; 22,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 7,24</t>
+          <t>-5,62; 7,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 7,22</t>
+          <t>-8,86; 6,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 9,01</t>
+          <t>-13,1; 9,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 8,18</t>
+          <t>-5,73; 7,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 8,22</t>
+          <t>-9,43; 7,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 11,55</t>
+          <t>-14,95; 11,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 5,13</t>
+          <t>-8,75; 5,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 8,05</t>
+          <t>-9,06; 8,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 8,95</t>
+          <t>-9,92; 8,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 5,65</t>
+          <t>-9,08; 5,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 9,54</t>
+          <t>-9,82; 9,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 10,75</t>
+          <t>-10,95; 10,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 0,25</t>
+          <t>-18,31; 0,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 17,24</t>
+          <t>-3,84; 18,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 20,96</t>
+          <t>-0,19; 21,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 0,26</t>
+          <t>-19,05; 0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 21,97</t>
+          <t>-4,04; 23,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 27,5</t>
+          <t>0,06; 28,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 3,02</t>
+          <t>-14,1; 2,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 13,61</t>
+          <t>-3,9; 12,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 6,87</t>
+          <t>-15,62; 6,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 3,33</t>
+          <t>-15,01; 3,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 16,42</t>
+          <t>-4,12; 15,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 8,18</t>
+          <t>-16,87; 8,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 5,67</t>
+          <t>-5,16; 5,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 3,55</t>
+          <t>-9,51; 3,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 1,33</t>
+          <t>-14,35; 2,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 6,2</t>
+          <t>-5,45; 5,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 4,07</t>
+          <t>-10,28; 3,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 1,78</t>
+          <t>-17,65; 2,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 3,75</t>
+          <t>-6,5; 3,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 6,8</t>
+          <t>-5,86; 6,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 5,63</t>
+          <t>-5,1; 6,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 4,22</t>
+          <t>-6,81; 3,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 8,33</t>
+          <t>-6,55; 8,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 6,69</t>
+          <t>-5,69; 7,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,97</t>
+          <t>-3,64; 0,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,82</t>
+          <t>-1,75; 3,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,35</t>
+          <t>-2,79; 3,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,06</t>
+          <t>-3,91; 1,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,4</t>
+          <t>-1,98; 4,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 4,0</t>
+          <t>-3,27; 4,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">

--- a/data/trans_bre/IP41-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Provincia-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,8 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,15 +531,13 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -563,27 +559,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -596,8 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -627,27 +611,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
           <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -660,42 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 12,08</t>
+          <t>-8,85; 12,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 10,53</t>
+          <t>-6,03; 9,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 12,8</t>
+          <t>-7,63; 12,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,61; 16,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 15,14</t>
+          <t>-6,61; 11,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 12,11</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-8,84; 16,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-8,32; 16,55</t>
         </is>
       </c>
     </row>
@@ -727,27 +691,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-1,85%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
           <t>11,44%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -760,42 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 4,73</t>
+          <t>-8,36; 4,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 11,03</t>
+          <t>-3,41; 10,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 16,2</t>
+          <t>0,08; 17,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,75; 4,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 5,0</t>
+          <t>-3,55; 13,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 13,6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-0,71; 22,28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>0,19; 23,75</t>
         </is>
       </c>
     </row>
@@ -827,27 +771,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>-1,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>-2,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -860,42 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 7,19</t>
+          <t>-6,32; 7,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 6,78</t>
+          <t>-8,94; 7,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 9,07</t>
+          <t>-13,63; 8,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,59; 7,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 7,99</t>
+          <t>-9,65; 8,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 7,92</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-14,95; 11,9</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-15,9; 10,31</t>
         </is>
       </c>
     </row>
@@ -927,27 +851,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>-0,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>-0,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -960,42 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 5,3</t>
+          <t>-8,93; 5,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 8,03</t>
+          <t>-8,84; 7,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 8,88</t>
+          <t>-8,65; 8,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,38; 5,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 5,84</t>
+          <t>-9,56; 8,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 9,56</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-10,95; 10,76</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-9,41; 9,8</t>
         </is>
       </c>
     </row>
@@ -1027,27 +931,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-8,56%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-8,56%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
           <t>12,12%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 0,11</t>
+          <t>-19,9; 0,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 18,09</t>
+          <t>-3,48; 18,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 21,21</t>
+          <t>0,58; 21,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-20,53; 0,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 0,12</t>
+          <t>-3,87; 24,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 23,9</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 28,39</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>1,07; 28,69</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1011,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-5,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-5,38%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
           <t>-4,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 2,85</t>
+          <t>-14,2; 2,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 12,76</t>
+          <t>-3,6; 13,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 6,67</t>
+          <t>-15,44; 7,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,99; 3,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 3,04</t>
+          <t>-3,8; 15,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 15,19</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-16,87; 8,05</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-16,86; 8,98</t>
         </is>
       </c>
     </row>
@@ -1227,27 +1091,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>-3,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,13%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
           <t>-8,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 5,22</t>
+          <t>-5,28; 5,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 3,43</t>
+          <t>-9,53; 3,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 2,17</t>
+          <t>-15,21; 2,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,59; 5,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 5,73</t>
+          <t>-10,39; 4,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 3,97</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-17,65; 2,94</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-18,53; 2,85</t>
         </is>
       </c>
     </row>
@@ -1327,27 +1171,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,35%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-1,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
           <t>0,59%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 3,46</t>
+          <t>-6,24; 3,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 6,83</t>
+          <t>-5,99; 6,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 6,2</t>
+          <t>-5,15; 5,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,62; 4,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 3,85</t>
+          <t>-6,73; 7,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 8,29</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-5,69; 7,36</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-5,66; 6,93</t>
         </is>
       </c>
     </row>
@@ -1427,27 +1251,17 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,4%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-1,4%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
           <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,99</t>
+          <t>-3,82; 1,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,55</t>
+          <t>-1,75; 3,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,94</t>
+          <t>-2,75; 3,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,11; 1,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,07</t>
+          <t>-1,92; 4,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,08</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 4,83</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-3,22; 4,73</t>
         </is>
       </c>
     </row>
@@ -1508,16 +1312,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>

--- a/data/trans_bre/IP41-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 12,93</t>
+          <t>-8,64; 13,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 9,61</t>
+          <t>-5,86; 10,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 12,64</t>
+          <t>-7,74; 12,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 16,36</t>
+          <t>-9,37; 16,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 11,08</t>
+          <t>-6,2; 11,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 16,55</t>
+          <t>-8,25; 16,69</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 4,4</t>
+          <t>-8,09; 3,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 10,71</t>
+          <t>-2,94; 10,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 17,28</t>
+          <t>0,95; 17,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 4,97</t>
+          <t>-8,55; 4,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 13,04</t>
+          <t>-3,19; 12,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 23,75</t>
+          <t>1,19; 23,9</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 7,19</t>
+          <t>-6,02; 7,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 7,11</t>
+          <t>-9,44; 7,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 8,28</t>
+          <t>-13,78; 9,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 7,77</t>
+          <t>-6,21; 8,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 8,1</t>
+          <t>-9,93; 8,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 10,31</t>
+          <t>-15,67; 11,55</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 5,08</t>
+          <t>-8,32; 5,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 7,54</t>
+          <t>-9,48; 8,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 8,21</t>
+          <t>-9,64; 8,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 5,6</t>
+          <t>-8,69; 5,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 8,97</t>
+          <t>-10,09; 9,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 9,8</t>
+          <t>-10,47; 10,75</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 0,45</t>
+          <t>-19,03; 0,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 18,85</t>
+          <t>-4,7; 17,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 21,08</t>
+          <t>-0,17; 20,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 0,23</t>
+          <t>-19,3; 0,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 24,28</t>
+          <t>-4,81; 21,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 28,69</t>
+          <t>-0,32; 27,5</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 2,82</t>
+          <t>-14,8; 3,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 13,06</t>
+          <t>-2,76; 13,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 7,39</t>
+          <t>-14,89; 6,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 3,17</t>
+          <t>-15,48; 3,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 15,84</t>
+          <t>-2,91; 16,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 8,98</t>
+          <t>-16,61; 8,18</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 5,14</t>
+          <t>-5,01; 5,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 3,76</t>
+          <t>-9,18; 3,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 2,07</t>
+          <t>-15,65; 1,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 5,71</t>
+          <t>-5,27; 6,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 4,33</t>
+          <t>-9,87; 4,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 2,85</t>
+          <t>-18,78; 1,78</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 3,94</t>
+          <t>-5,92; 3,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 6,25</t>
+          <t>-5,92; 6,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 5,93</t>
+          <t>-4,93; 5,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 4,4</t>
+          <t>-6,25; 4,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 7,63</t>
+          <t>-6,66; 8,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 6,93</t>
+          <t>-5,35; 6,69</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,04</t>
+          <t>-3,81; 0,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,58</t>
+          <t>-1,89; 3,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,89</t>
+          <t>-2,81; 3,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 1,13</t>
+          <t>-4,06; 1,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,14</t>
+          <t>-2,11; 4,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,73</t>
+          <t>-3,31; 4,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP41-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Provincia-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.15504624140217</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.025358702449875</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.39906068308724</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.02515028206810647</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.02226194449080231</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.02824067919123045</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,64; 13,04</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,86; 10,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,74; 12,78</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-9,37; 16,2</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-6,2; 11,56</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-8,25; 16,69</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.637176525376505</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.861644357472422</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.738878778416855</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.09368150357991982</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.06200248430218898</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.08253491760731912</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>13.04128547012539</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.00287140432881</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12.78218445701715</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.161966490556108</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1156162585390458</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1668987544022964</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,92</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,88</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,09; 3,81</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,94; 10,52</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,95; 17,39</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-8,55; 4,26</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-3,19; 12,67</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 23,9</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.711424041379506</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.920709828372126</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>8.879699822392285</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.01853309782985795</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04487844944400689</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1144478025845131</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,65%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.093852768871765</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.938538300416794</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9499338116046403</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.08546535869007944</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.03191011676850399</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.01185445483318026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,02; 7,24</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,44; 7,22</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-13,78; 9,01</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,21; 8,18</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-9,93; 8,22</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-15,67; 11,55</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.808429996527921</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.51898210009939</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>17.38606251201657</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.04255053599054286</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1266711875218707</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2390081643967073</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +767,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,6%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,84%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-0,03%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.7733175347434118</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.01845466280851</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.212149304689903</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.008252003415655192</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.01113694481981591</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.02647994305655285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,32; 5,13</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-9,48; 8,05</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-9,64; 8,95</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,69; 5,65</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-10,09; 9,54</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-10,47; 10,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.018510136082293</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-9.442861036458188</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-13.77621138647061</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.0621164657527738</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.09930701096664618</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1567419690432337</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.239297804585723</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.221792743665365</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.009974566855043</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.08180319776946361</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.08219021403530326</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1155201272592398</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-8,15</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-8,56%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-19,03; 0,25</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,7; 17,24</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,17; 20,96</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-19,3; 0,26</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-4,81; 21,97</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,32; 27,5</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.493771962350099</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.7419269752509283</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.02349172958118206</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.0159945853413059</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.008354780478868963</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.0002667251225371469</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-4,99</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5,04</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-4,22</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-5,38%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-4,81%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-8.323005872745695</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-9.483458008198422</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-9.641685491100224</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.08690010328573719</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1008994881944219</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1047174983029672</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-14,8; 3,02</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-2,76; 13,61</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-14,89; 6,87</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-15,48; 3,33</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-2,91; 16,42</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-16,61; 8,18</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.127662761620842</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.050937767022447</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.951477150606967</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.05645496846090042</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.09539056167912435</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1074745454873737</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,237 +931,407 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-2,81</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-6,51</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,13%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-8,27%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-8.147644197272175</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>6.999278143582677</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>10.16122354318779</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.08555409617236145</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.08267045142381355</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1211854081138322</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-5,01; 5,67</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-9,18; 3,55</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-15,65; 1,33</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-5,27; 6,2</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-9,87; 4,07</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-18,78; 1,78</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-19.026572905816</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.700595110539864</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.1740446814919911</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.1929506994318713</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.04809995564187009</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.003206887876149873</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.246907895186104</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>17.23877727011742</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>20.96453760501103</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.002570648270036446</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2197223184261975</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2750076052443843</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-1,35%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-5,92; 3,75</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-5,92; 6,8</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-4,93; 5,63</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-6,25; 4,22</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-6,66; 8,33</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-5,35; 6,69</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>-4.994340028594236</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>5.039260218914976</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-4.219325173673749</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.05376211287705607</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.05677759845684591</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.04808293056136799</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,4%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-14.79811471895857</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-2.757151352215482</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-14.88925959646282</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.1547909496975007</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.02912216818753421</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.1661029107314367</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>-3,81; 0,97</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-1,89; 3,82</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-2,81; 3,35</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>-4,06; 1,06</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 4,4</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-3,31; 4,0</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3.016246536588237</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>13.60875090305856</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>6.873489402480283</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.03330752172335346</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1641802750723158</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.08176742652339845</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.2260256247115455</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-2.810516755479098</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-6.507639913272922</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.002442993393164463</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.03129836904933295</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.08274686414600824</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-5.014299913598927</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-9.179534524865401</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-15.64760927989398</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.05266239713238615</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.09865648430788365</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.1878271570824378</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>5.670753128199042</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.548286318444586</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.332187932915593</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.06199378597451111</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.0407317557298763</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.01781797613393596</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-1.255671232757083</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0.2850655460773566</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.5220845647231465</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.01354516189453731</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.003321076030929177</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.005918752341440438</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-5.924716355716177</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-5.922343476810431</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-4.931630992032381</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.06245922482171102</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.06655621653785287</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.05345707107611698</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>3.749013524524151</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>6.802747327468611</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>5.627137177474893</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.0421913241453836</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.08328324978058635</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.06685150210439862</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-1.291350389372303</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.887488743761522</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.438067261686359</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-0.01397804185036947</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0.01005256970818911</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0.005230318811633617</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-3.807112858259318</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-1.890082802216952</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-2.810084340435331</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-0.04060615843134109</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-0.02114604784160384</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>-0.03313003466145011</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.9670390298034258</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.823869576491322</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>3.349075401492358</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.01059845365509916</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0.04397412199349154</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0.03997637458596782</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1313,17 +1340,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
